--- a/public/dashboard_financeiro.xlsx
+++ b/public/dashboard_financeiro.xlsx
@@ -414,6 +414,12 @@
           <tx>
             <strRef>
               <f>'Fluxo Mensal'!B4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Entradas</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -427,11 +433,61 @@
           <cat>
             <numRef>
               <f>'Fluxo Mensal'!$A$5:$A$11</f>
+              <numCache>
+                <formatCode>mmm/yyyy</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>46082</v>
+                </pt>
+                <pt idx="1">
+                  <v>46113</v>
+                </pt>
+                <pt idx="2">
+                  <v>46143</v>
+                </pt>
+                <pt idx="3">
+                  <v>46174</v>
+                </pt>
+                <pt idx="4">
+                  <v>46204</v>
+                </pt>
+                <pt idx="5">
+                  <v>46235</v>
+                </pt>
+                <pt idx="6">
+                  <v>46266</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Fluxo Mensal'!$B$5:$B$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>17510.88</v>
+                </pt>
+                <pt idx="2">
+                  <v>13227.69</v>
+                </pt>
+                <pt idx="3">
+                  <v>10106.95</v>
+                </pt>
+                <pt idx="4">
+                  <v>15254.72</v>
+                </pt>
+                <pt idx="5">
+                  <v>14949.33</v>
+                </pt>
+                <pt idx="6">
+                  <v>11926.98</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -441,6 +497,12 @@
           <tx>
             <strRef>
               <f>'Fluxo Mensal'!C4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Saídas</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -454,11 +516,61 @@
           <cat>
             <numRef>
               <f>'Fluxo Mensal'!$A$5:$A$11</f>
+              <numCache>
+                <formatCode>mmm/yyyy</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>46082</v>
+                </pt>
+                <pt idx="1">
+                  <v>46113</v>
+                </pt>
+                <pt idx="2">
+                  <v>46143</v>
+                </pt>
+                <pt idx="3">
+                  <v>46174</v>
+                </pt>
+                <pt idx="4">
+                  <v>46204</v>
+                </pt>
+                <pt idx="5">
+                  <v>46235</v>
+                </pt>
+                <pt idx="6">
+                  <v>46266</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Fluxo Mensal'!$C$5:$C$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>3978.99</v>
+                </pt>
+                <pt idx="2">
+                  <v>9067.969999999999</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>24986.93</v>
+                </pt>
+                <pt idx="5">
+                  <v>6810.780000000001</v>
+                </pt>
+                <pt idx="6">
+                  <v>16794.63</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -544,6 +656,12 @@
           <tx>
             <strRef>
               <f>'Fluxo Mensal'!B4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Entradas</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -557,11 +675,61 @@
           <cat>
             <numRef>
               <f>'Fluxo Mensal'!$A$5:$A$11</f>
+              <numCache>
+                <formatCode>mmm/yyyy</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>46082</v>
+                </pt>
+                <pt idx="1">
+                  <v>46113</v>
+                </pt>
+                <pt idx="2">
+                  <v>46143</v>
+                </pt>
+                <pt idx="3">
+                  <v>46174</v>
+                </pt>
+                <pt idx="4">
+                  <v>46204</v>
+                </pt>
+                <pt idx="5">
+                  <v>46235</v>
+                </pt>
+                <pt idx="6">
+                  <v>46266</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Fluxo Mensal'!$B$5:$B$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>17510.88</v>
+                </pt>
+                <pt idx="2">
+                  <v>13227.69</v>
+                </pt>
+                <pt idx="3">
+                  <v>10106.95</v>
+                </pt>
+                <pt idx="4">
+                  <v>15254.72</v>
+                </pt>
+                <pt idx="5">
+                  <v>14949.33</v>
+                </pt>
+                <pt idx="6">
+                  <v>11926.98</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -571,6 +739,12 @@
           <tx>
             <strRef>
               <f>'Fluxo Mensal'!C4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Saídas</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -584,11 +758,61 @@
           <cat>
             <numRef>
               <f>'Fluxo Mensal'!$A$5:$A$11</f>
+              <numCache>
+                <formatCode>mmm/yyyy</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>46082</v>
+                </pt>
+                <pt idx="1">
+                  <v>46113</v>
+                </pt>
+                <pt idx="2">
+                  <v>46143</v>
+                </pt>
+                <pt idx="3">
+                  <v>46174</v>
+                </pt>
+                <pt idx="4">
+                  <v>46204</v>
+                </pt>
+                <pt idx="5">
+                  <v>46235</v>
+                </pt>
+                <pt idx="6">
+                  <v>46266</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Fluxo Mensal'!$C$5:$C$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>3978.99</v>
+                </pt>
+                <pt idx="2">
+                  <v>9067.969999999999</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>24986.93</v>
+                </pt>
+                <pt idx="5">
+                  <v>6810.780000000001</v>
+                </pt>
+                <pt idx="6">
+                  <v>16794.63</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -673,6 +897,12 @@
           <tx>
             <strRef>
               <f>'Fluxo Mensal'!E4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Saldo Acumulado</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -701,11 +931,61 @@
           <cat>
             <numRef>
               <f>'Fluxo Mensal'!$A$5:$A$11</f>
+              <numCache>
+                <formatCode>mmm/yyyy</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>46082</v>
+                </pt>
+                <pt idx="1">
+                  <v>46113</v>
+                </pt>
+                <pt idx="2">
+                  <v>46143</v>
+                </pt>
+                <pt idx="3">
+                  <v>46174</v>
+                </pt>
+                <pt idx="4">
+                  <v>46204</v>
+                </pt>
+                <pt idx="5">
+                  <v>46235</v>
+                </pt>
+                <pt idx="6">
+                  <v>46266</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Fluxo Mensal'!$E$5:$E$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="7"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>13531.89</v>
+                </pt>
+                <pt idx="2">
+                  <v>17691.61</v>
+                </pt>
+                <pt idx="3">
+                  <v>27798.56</v>
+                </pt>
+                <pt idx="4">
+                  <v>18066.35</v>
+                </pt>
+                <pt idx="5">
+                  <v>26204.9</v>
+                </pt>
+                <pt idx="6">
+                  <v>21337.25</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -794,13 +1074,56 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'DRE'!$A$6:$A$11</f>
-            </numRef>
+              <strCache>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>Aluguel</v>
+                </pt>
+                <pt idx="1">
+                  <v>Fornecedor</v>
+                </pt>
+                <pt idx="2">
+                  <v>Imposto</v>
+                </pt>
+                <pt idx="3">
+                  <v>Manutenção</v>
+                </pt>
+                <pt idx="4">
+                  <v>Marketing</v>
+                </pt>
+                <pt idx="5">
+                  <v>Salário</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'DRE'!$B$6:$B$11</f>
+              <numCache>
+                <formatCode>"R$" #,##0.00</formatCode>
+                <ptCount val="6"/>
+                <pt idx="0">
+                  <v>26246.34</v>
+                </pt>
+                <pt idx="1">
+                  <v>46762.05</v>
+                </pt>
+                <pt idx="2">
+                  <v>68429.45</v>
+                </pt>
+                <pt idx="3">
+                  <v>28808.36</v>
+                </pt>
+                <pt idx="4">
+                  <v>25904.33</v>
+                </pt>
+                <pt idx="5">
+                  <v>47849.25</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -1359,19 +1682,19 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7">
         <f>'Fluxo Mensal'!B12</f>
-        <v/>
+        <v>82976.55</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="10">
         <f>'Fluxo Mensal'!C12</f>
-        <v/>
+        <v>61639.3</v>
       </c>
       <c r="E5" s="8" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="11">
         <f>'Fluxo Mensal'!D12</f>
-        <v/>
+        <v>21337.25</v>
       </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="9" t="n"/>
@@ -1402,19 +1725,19 @@
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="7">
         <f>'Contas a Pagar e Receber'!D5</f>
-        <v/>
+        <v>199712.9</v>
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="10">
         <f>'Contas a Pagar e Receber'!D6</f>
-        <v/>
+        <v>177687.16</v>
       </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="11">
         <f>DRE!B14</f>
-        <v/>
+        <v>61963.98</v>
       </c>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="9" t="n"/>
@@ -7186,19 +7509,19 @@
       </c>
       <c r="B5" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A5,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A5,1))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C5" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A5,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A5,1))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D5" s="16">
         <f>B5-C5</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E5" s="16">
         <f>D5</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -7207,19 +7530,19 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A6,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A6,1))</f>
-        <v/>
+        <v>17510.88</v>
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A6,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A6,1))</f>
-        <v/>
+        <v>3978.99</v>
       </c>
       <c r="D6" s="16">
         <f>B6-C6</f>
-        <v/>
+        <v>13531.89</v>
       </c>
       <c r="E6" s="16">
         <f>E5+D6</f>
-        <v/>
+        <v>13531.89</v>
       </c>
     </row>
     <row r="7">
@@ -7228,19 +7551,19 @@
       </c>
       <c r="B7" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A7,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A7,1))</f>
-        <v/>
+        <v>13227.69</v>
       </c>
       <c r="C7" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A7,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A7,1))</f>
-        <v/>
+        <v>9067.97</v>
       </c>
       <c r="D7" s="16">
         <f>B7-C7</f>
-        <v/>
+        <v>4159.72</v>
       </c>
       <c r="E7" s="16">
         <f>E6+D7</f>
-        <v/>
+        <v>17691.61</v>
       </c>
     </row>
     <row r="8">
@@ -7249,19 +7572,19 @@
       </c>
       <c r="B8" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A8,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A8,1))</f>
-        <v/>
+        <v>10106.95</v>
       </c>
       <c r="C8" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A8,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A8,1))</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D8" s="16">
         <f>B8-C8</f>
-        <v/>
+        <v>10106.95</v>
       </c>
       <c r="E8" s="16">
         <f>E7+D8</f>
-        <v/>
+        <v>27798.56</v>
       </c>
     </row>
     <row r="9">
@@ -7270,19 +7593,19 @@
       </c>
       <c r="B9" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A9,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A9,1))</f>
-        <v/>
+        <v>15254.72</v>
       </c>
       <c r="C9" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A9,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A9,1))</f>
-        <v/>
+        <v>24986.93</v>
       </c>
       <c r="D9" s="16">
         <f>B9-C9</f>
-        <v/>
+        <v>-9732.21</v>
       </c>
       <c r="E9" s="16">
         <f>E8+D9</f>
-        <v/>
+        <v>18066.35</v>
       </c>
     </row>
     <row r="10">
@@ -7291,19 +7614,19 @@
       </c>
       <c r="B10" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A10,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A10,1))</f>
-        <v/>
+        <v>14949.33</v>
       </c>
       <c r="C10" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A10,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A10,1))</f>
-        <v/>
+        <v>6810.78</v>
       </c>
       <c r="D10" s="16">
         <f>B10-C10</f>
-        <v/>
+        <v>8138.55</v>
       </c>
       <c r="E10" s="16">
         <f>E9+D10</f>
-        <v/>
+        <v>26204.9</v>
       </c>
     </row>
     <row r="11">
@@ -7312,19 +7635,19 @@
       </c>
       <c r="B11" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A11,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A11,1))</f>
-        <v/>
+        <v>11926.98</v>
       </c>
       <c r="C11" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pago",Dados!$A$2:$A$201,"&gt;="&amp;A11,Dados!$A$2:$A$201,"&lt;"&amp;EDATE(A11,1))</f>
-        <v/>
+        <v>16794.63</v>
       </c>
       <c r="D11" s="16">
         <f>B11-C11</f>
-        <v/>
+        <v>-4867.65</v>
       </c>
       <c r="E11" s="16">
         <f>E10+D11</f>
-        <v/>
+        <v>21337.25</v>
       </c>
     </row>
     <row r="12">
@@ -7335,15 +7658,15 @@
       </c>
       <c r="B12" s="19">
         <f>SUM(B5:B11)</f>
-        <v/>
+        <v>82976.55</v>
       </c>
       <c r="C12" s="19">
         <f>SUM(C5:C11)</f>
-        <v/>
+        <v>61639.3</v>
       </c>
       <c r="D12" s="19">
         <f>SUM(D5:D11)</f>
-        <v/>
+        <v>21337.25</v>
       </c>
       <c r="E12" s="20" t="n"/>
     </row>
@@ -7446,15 +7769,15 @@
       </c>
       <c r="B5" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Pendente")</f>
-        <v/>
+        <v>86550.82</v>
       </c>
       <c r="C5" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada",Dados!$F$2:$F$201,"Atrasado")</f>
-        <v/>
+        <v>113162.08</v>
       </c>
       <c r="D5" s="25">
         <f>B5+C5</f>
-        <v/>
+        <v>199712.9</v>
       </c>
     </row>
     <row r="6">
@@ -7465,15 +7788,15 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Pendente")</f>
-        <v/>
+        <v>84201.8</v>
       </c>
       <c r="C6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$F$2:$F$201,"Atrasado")</f>
-        <v/>
+        <v>93485.36</v>
       </c>
       <c r="D6" s="25">
         <f>B6+C6</f>
-        <v/>
+        <v>177687.16</v>
       </c>
     </row>
     <row r="7">
@@ -7486,7 +7809,7 @@
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="28">
         <f>D5-D6</f>
-        <v/>
+        <v>22025.74</v>
       </c>
     </row>
     <row r="10">
@@ -10620,7 +10943,7 @@
       </c>
       <c r="B4" s="33">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Entrada")</f>
-        <v/>
+        <v>305963.76</v>
       </c>
     </row>
     <row r="5">
@@ -10638,7 +10961,7 @@
       </c>
       <c r="B6" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Aluguel")</f>
-        <v/>
+        <v>26246.34</v>
       </c>
     </row>
     <row r="7">
@@ -10649,7 +10972,7 @@
       </c>
       <c r="B7" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Fornecedor")</f>
-        <v/>
+        <v>46762.05</v>
       </c>
     </row>
     <row r="8">
@@ -10660,7 +10983,7 @@
       </c>
       <c r="B8" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Imposto")</f>
-        <v/>
+        <v>68429.45</v>
       </c>
     </row>
     <row r="9">
@@ -10671,7 +10994,7 @@
       </c>
       <c r="B9" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Manutenção")</f>
-        <v/>
+        <v>28808.36</v>
       </c>
     </row>
     <row r="10">
@@ -10682,7 +11005,7 @@
       </c>
       <c r="B10" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Marketing")</f>
-        <v/>
+        <v>25904.33</v>
       </c>
     </row>
     <row r="11">
@@ -10693,7 +11016,7 @@
       </c>
       <c r="B11" s="16">
         <f>SUMIFS(Dados!$E$2:$E$201,Dados!$D$2:$D$201,"Saída",Dados!$C$2:$C$201,"Salário")</f>
-        <v/>
+        <v>47849.25</v>
       </c>
     </row>
     <row r="12">
@@ -10704,7 +11027,7 @@
       </c>
       <c r="B12" s="35">
         <f>SUM(B6:B11)</f>
-        <v/>
+        <v>243999.78</v>
       </c>
     </row>
     <row r="14">
@@ -10715,7 +11038,7 @@
       </c>
       <c r="B14" s="37">
         <f>B4-B12</f>
-        <v/>
+        <v>61963.98</v>
       </c>
     </row>
     <row r="15">
@@ -10726,7 +11049,7 @@
       </c>
       <c r="B15" s="39">
         <f>B14/B4</f>
-        <v/>
+        <v>0.2025206515</v>
       </c>
     </row>
   </sheetData>
